--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.04. Islak İşlem Kontrol Formu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.04. Islak İşlem Kontrol Formu.xlsx
@@ -274,7 +274,7 @@
     <t>Approved By</t>
   </si>
   <si>
-    <t>EG.QA.FRM.04.04</t>
+    <t>EMS.QA.FRM.04.04</t>
   </si>
 </sst>
 </file>
